--- a/importSpec.xlsx
+++ b/importSpec.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28521"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28025"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF3DF627-5CA5-4423-8BC7-1BC83F4777A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sudarshan.sambamurth\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B6137A0-3061-4209-9241-45BB919C4579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,55 +36,37 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>FileName</t>
-  </si>
-  <si>
-    <t>PRODUCT MATRIX FOR GXXX SENSORS</t>
-  </si>
-  <si>
-    <t>20086276_AM.xlsx</t>
-  </si>
-  <si>
-    <t>ER-20021994</t>
-  </si>
-  <si>
-    <t>Option Specific Sourcing (OSS)Item OCD Rules</t>
-  </si>
-  <si>
-    <t>ER-20021994_AJ.pdf</t>
-  </si>
-  <si>
-    <t>ER-20095313</t>
-  </si>
-  <si>
-    <t>FLANGED ASSY, G-SERIES</t>
-  </si>
-  <si>
-    <t>ER-20095313_AC.pdf</t>
-  </si>
-  <si>
-    <t>ER-20096208</t>
-  </si>
-  <si>
-    <t>G SERIES CA, PC AND WELD ROD SELECTION</t>
-  </si>
-  <si>
-    <t>ER-20096208_AO.pdf</t>
+    <t xml:space="preserve"> Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> FileName</t>
+  </si>
+  <si>
+    <t>DOC-00007</t>
+  </si>
+  <si>
+    <t>Documents</t>
+  </si>
+  <si>
+    <t>DOC-00007.txt</t>
+  </si>
+  <si>
+    <t>DOC-00008</t>
+  </si>
+  <si>
+    <t>DOC-00008.txt</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -444,16 +431,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.140625" customWidth="1"/>
-    <col min="2" max="2" width="41.5703125" customWidth="1"/>
-    <col min="3" max="3" width="39.28515625" customWidth="1"/>
+    <col min="1" max="1" width="13.1796875" customWidth="1"/>
+    <col min="2" max="2" width="41.54296875" customWidth="1"/>
+    <col min="3" max="3" width="39.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -464,48 +450,26 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2">
-        <v>20086726</v>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
       </c>
       <c r="C3" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
